--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F089633-D4C6-42D3-8E8B-F51D16616712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4765E5BC-A3E1-46A7-9EA2-C27FD8801629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5488,6 +5488,75 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_coal_st_G100000100731-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100727-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100728-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000106102-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100001000616_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110372_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000104991-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107654_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100725-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100732-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100735-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107652_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100730-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107653_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100729-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100726-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000100722_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105928_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100733-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000107651_rf</t>
   </si>
   <si>
@@ -5500,28 +5569,7 @@
     <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_st_G100000100731-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100727-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100728-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000106102-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110372_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100001000616_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107652_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100730-CHP_rf</t>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
@@ -5533,10 +5581,7 @@
     <t>ep_coal_st_G100000107650_rf</t>
   </si>
   <si>
-    <t>ep_coal_st_G100000105928_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100733-CHP_rf</t>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
   </si>
   <si>
     <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
@@ -5545,58 +5590,13 @@
     <t>ep_coal_sc_G100000107859_rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000105920_rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107653_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100729-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000100722_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100726-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100725-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100735-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100732-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107654_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000104991-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6909,7 +6909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{704136F6-BFA3-4DD6-A129-F52C98942E9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{560D72D0-D1D5-40E7-9A34-9E570C7BAD83}">
   <dimension ref="B2:AG1615"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44008,7 +44008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE38C32-4174-4699-86A4-4FEF3ECB3DCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3A40AE-D3A1-4288-B720-6C6199E5B5CB}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -58269,7 +58269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9525E74A-4A67-4D1F-A60D-748281D66595}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF20344-3800-486B-A177-0813617C1C45}">
   <dimension ref="B2:Q248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61746,7 +61746,7 @@
         <v>1801</v>
       </c>
       <c r="P212" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -61760,7 +61760,7 @@
         <v>1802</v>
       </c>
       <c r="P213" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -61788,10 +61788,10 @@
         <v>1804</v>
       </c>
       <c r="P215" t="s">
-        <v>1785</v>
+        <v>1793</v>
       </c>
       <c r="Q215">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -61802,7 +61802,7 @@
         <v>1805</v>
       </c>
       <c r="P216" t="s">
-        <v>1786</v>
+        <v>1769</v>
       </c>
       <c r="Q216">
         <v>0.85</v>
@@ -61816,7 +61816,7 @@
         <v>1806</v>
       </c>
       <c r="P217" t="s">
-        <v>1786</v>
+        <v>1760</v>
       </c>
       <c r="Q217">
         <v>0.85</v>
@@ -61830,10 +61830,10 @@
         <v>1807</v>
       </c>
       <c r="P218" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="Q218">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="219" spans="14:17" x14ac:dyDescent="0.45">
@@ -61844,10 +61844,10 @@
         <v>1808</v>
       </c>
       <c r="P219" t="s">
-        <v>1793</v>
+        <v>1762</v>
       </c>
       <c r="Q219">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -61858,10 +61858,10 @@
         <v>1809</v>
       </c>
       <c r="P220" t="s">
-        <v>1760</v>
+        <v>1795</v>
       </c>
       <c r="Q220">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -61872,10 +61872,10 @@
         <v>1810</v>
       </c>
       <c r="P221" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="Q221">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="222" spans="14:17" x14ac:dyDescent="0.45">
@@ -61886,7 +61886,7 @@
         <v>1811</v>
       </c>
       <c r="P222" t="s">
-        <v>1781</v>
+        <v>1793</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -61900,7 +61900,7 @@
         <v>1812</v>
       </c>
       <c r="P223" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -61914,10 +61914,10 @@
         <v>1813</v>
       </c>
       <c r="P224" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="Q224">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="225" spans="14:17" x14ac:dyDescent="0.45">
@@ -61928,7 +61928,7 @@
         <v>1814</v>
       </c>
       <c r="P225" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -61942,7 +61942,7 @@
         <v>1815</v>
       </c>
       <c r="P226" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -61956,7 +61956,7 @@
         <v>1816</v>
       </c>
       <c r="P227" t="s">
-        <v>1769</v>
+        <v>1781</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -61984,10 +61984,10 @@
         <v>1818</v>
       </c>
       <c r="P229" t="s">
-        <v>1761</v>
+        <v>1781</v>
       </c>
       <c r="Q229">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -61998,7 +61998,7 @@
         <v>1819</v>
       </c>
       <c r="P230" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -62012,7 +62012,7 @@
         <v>1820</v>
       </c>
       <c r="P231" t="s">
-        <v>1769</v>
+        <v>1786</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -62026,10 +62026,10 @@
         <v>1821</v>
       </c>
       <c r="P232" t="s">
-        <v>1796</v>
+        <v>1786</v>
       </c>
       <c r="Q232">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="233" spans="14:17" x14ac:dyDescent="0.45">
@@ -62040,10 +62040,10 @@
         <v>1822</v>
       </c>
       <c r="P233" t="s">
-        <v>1792</v>
+        <v>1769</v>
       </c>
       <c r="Q233">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -62054,7 +62054,7 @@
         <v>1823</v>
       </c>
       <c r="P234" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -62068,7 +62068,7 @@
         <v>1824</v>
       </c>
       <c r="P235" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q235">
         <v>0.85</v>
@@ -62082,7 +62082,7 @@
         <v>1825</v>
       </c>
       <c r="P236" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -62110,7 +62110,7 @@
         <v>1827</v>
       </c>
       <c r="P238" t="s">
-        <v>1792</v>
+        <v>1785</v>
       </c>
       <c r="Q238">
         <v>0.95</v>
@@ -62138,10 +62138,10 @@
         <v>1829</v>
       </c>
       <c r="P240" t="s">
-        <v>1786</v>
+        <v>1797</v>
       </c>
       <c r="Q240">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -62152,7 +62152,7 @@
         <v>1830</v>
       </c>
       <c r="P241" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -62166,7 +62166,7 @@
         <v>1831</v>
       </c>
       <c r="P242" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -62180,10 +62180,10 @@
         <v>1832</v>
       </c>
       <c r="P243" t="s">
-        <v>1781</v>
+        <v>1792</v>
       </c>
       <c r="Q243">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="244" spans="14:17" x14ac:dyDescent="0.45">
@@ -62194,7 +62194,7 @@
         <v>1833</v>
       </c>
       <c r="P244" t="s">
-        <v>1782</v>
+        <v>1761</v>
       </c>
       <c r="Q244">
         <v>0.95</v>
@@ -62208,7 +62208,7 @@
         <v>1834</v>
       </c>
       <c r="P245" t="s">
-        <v>1793</v>
+        <v>1782</v>
       </c>
       <c r="Q245">
         <v>0.85</v>
@@ -62222,7 +62222,7 @@
         <v>1835</v>
       </c>
       <c r="P246" t="s">
-        <v>1771</v>
+        <v>1796</v>
       </c>
       <c r="Q246">
         <v>0.95</v>
@@ -62236,10 +62236,10 @@
         <v>1836</v>
       </c>
       <c r="P247" t="s">
-        <v>1795</v>
+        <v>1769</v>
       </c>
       <c r="Q247">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -62250,7 +62250,7 @@
         <v>1837</v>
       </c>
       <c r="P248" t="s">
-        <v>1762</v>
+        <v>1792</v>
       </c>
       <c r="Q248">
         <v>0.95</v>
@@ -62262,7 +62262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A325474B-0BB9-4272-A69D-70157A9804E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCF994E-61AA-425E-B6B6-87ACF378C36E}">
   <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4765E5BC-A3E1-46A7-9EA2-C27FD8801629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5854CE2-BE94-4343-A1C9-4A53E3D2B2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5488,115 +5488,115 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_coal_st_G100000105928_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100733-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000100731-CHP_rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107651_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100734-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107649_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000111550-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107650_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100001000616_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000106102-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110372_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100726-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107653_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100729-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000100722_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000107859_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105920_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000100727-CHP_rf</t>
   </si>
   <si>
     <t>ep_coal_st_G100000100728-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_sc_G100000106102-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100001000616_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110372_rf</t>
+    <t>ep_coal_st_G100000100730-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107652_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100732-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100725-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100735-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000104991-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107654_rf</t>
   </si>
   <si>
     <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
   </si>
   <si>
+    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
+  </si>
+  <si>
     <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
   </si>
   <si>
-    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
-  </si>
-  <si>
     <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000104991-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107654_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100725-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100732-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100735-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107652_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100730-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107653_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100729-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100726-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000100722_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105928_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100733-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107651_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107649_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100734-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000111550-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107650_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000107859_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105920_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6909,7 +6909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{560D72D0-D1D5-40E7-9A34-9E570C7BAD83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C846FD6-271F-4F66-AF33-82A71C8B444F}">
   <dimension ref="B2:AG1615"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44008,7 +44008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3A40AE-D3A1-4288-B720-6C6199E5B5CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65935634-3F7D-4564-899F-4EB106F3448F}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -58269,7 +58269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF20344-3800-486B-A177-0813617C1C45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2E71F3-42DB-44CC-880E-1CDB0F36164D}">
   <dimension ref="B2:Q248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61746,7 +61746,7 @@
         <v>1801</v>
       </c>
       <c r="P212" t="s">
-        <v>1786</v>
+        <v>1769</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -61788,10 +61788,10 @@
         <v>1804</v>
       </c>
       <c r="P215" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="Q215">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -61802,7 +61802,7 @@
         <v>1805</v>
       </c>
       <c r="P216" t="s">
-        <v>1769</v>
+        <v>1781</v>
       </c>
       <c r="Q216">
         <v>0.85</v>
@@ -61816,7 +61816,7 @@
         <v>1806</v>
       </c>
       <c r="P217" t="s">
-        <v>1760</v>
+        <v>1786</v>
       </c>
       <c r="Q217">
         <v>0.85</v>
@@ -61830,10 +61830,10 @@
         <v>1807</v>
       </c>
       <c r="P218" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="Q218">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="219" spans="14:17" x14ac:dyDescent="0.45">
@@ -61844,7 +61844,7 @@
         <v>1808</v>
       </c>
       <c r="P219" t="s">
-        <v>1762</v>
+        <v>1785</v>
       </c>
       <c r="Q219">
         <v>0.95</v>
@@ -61858,7 +61858,7 @@
         <v>1809</v>
       </c>
       <c r="P220" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="Q220">
         <v>0.95</v>
@@ -61872,10 +61872,10 @@
         <v>1810</v>
       </c>
       <c r="P221" t="s">
-        <v>1771</v>
+        <v>1785</v>
       </c>
       <c r="Q221">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="222" spans="14:17" x14ac:dyDescent="0.45">
@@ -61886,7 +61886,7 @@
         <v>1811</v>
       </c>
       <c r="P222" t="s">
-        <v>1793</v>
+        <v>1781</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -61900,7 +61900,7 @@
         <v>1812</v>
       </c>
       <c r="P223" t="s">
-        <v>1781</v>
+        <v>1769</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -61914,7 +61914,7 @@
         <v>1813</v>
       </c>
       <c r="P224" t="s">
-        <v>1786</v>
+        <v>1793</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -61928,7 +61928,7 @@
         <v>1814</v>
       </c>
       <c r="P225" t="s">
-        <v>1786</v>
+        <v>1760</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -61984,7 +61984,7 @@
         <v>1818</v>
       </c>
       <c r="P229" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q229">
         <v>0.85</v>
@@ -61998,7 +61998,7 @@
         <v>1819</v>
       </c>
       <c r="P230" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -62012,10 +62012,10 @@
         <v>1820</v>
       </c>
       <c r="P231" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="Q231">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="232" spans="14:17" x14ac:dyDescent="0.45">
@@ -62026,7 +62026,7 @@
         <v>1821</v>
       </c>
       <c r="P232" t="s">
-        <v>1786</v>
+        <v>1769</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -62040,10 +62040,10 @@
         <v>1822</v>
       </c>
       <c r="P233" t="s">
-        <v>1769</v>
+        <v>1792</v>
       </c>
       <c r="Q233">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -62054,10 +62054,10 @@
         <v>1823</v>
       </c>
       <c r="P234" t="s">
-        <v>1786</v>
+        <v>1761</v>
       </c>
       <c r="Q234">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -62068,7 +62068,7 @@
         <v>1824</v>
       </c>
       <c r="P235" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q235">
         <v>0.85</v>
@@ -62082,7 +62082,7 @@
         <v>1825</v>
       </c>
       <c r="P236" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -62110,10 +62110,10 @@
         <v>1827</v>
       </c>
       <c r="P238" t="s">
-        <v>1785</v>
+        <v>1781</v>
       </c>
       <c r="Q238">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="239" spans="14:17" x14ac:dyDescent="0.45">
@@ -62138,10 +62138,10 @@
         <v>1829</v>
       </c>
       <c r="P240" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="Q240">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -62152,7 +62152,7 @@
         <v>1830</v>
       </c>
       <c r="P241" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -62166,7 +62166,7 @@
         <v>1831</v>
       </c>
       <c r="P242" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q242">
         <v>0.85</v>
@@ -62180,10 +62180,10 @@
         <v>1832</v>
       </c>
       <c r="P243" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="Q243">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="244" spans="14:17" x14ac:dyDescent="0.45">
@@ -62194,10 +62194,10 @@
         <v>1833</v>
       </c>
       <c r="P244" t="s">
-        <v>1761</v>
+        <v>1781</v>
       </c>
       <c r="Q244">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="245" spans="14:17" x14ac:dyDescent="0.45">
@@ -62211,7 +62211,7 @@
         <v>1782</v>
       </c>
       <c r="Q245">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -62222,7 +62222,7 @@
         <v>1835</v>
       </c>
       <c r="P246" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="Q246">
         <v>0.95</v>
@@ -62236,10 +62236,10 @@
         <v>1836</v>
       </c>
       <c r="P247" t="s">
-        <v>1769</v>
+        <v>1762</v>
       </c>
       <c r="Q247">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -62250,7 +62250,7 @@
         <v>1837</v>
       </c>
       <c r="P248" t="s">
-        <v>1792</v>
+        <v>1771</v>
       </c>
       <c r="Q248">
         <v>0.95</v>
@@ -62262,7 +62262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCF994E-61AA-425E-B6B6-87ACF378C36E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A12C32-7A7F-4AB2-9779-180FBF0FA173}">
   <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5854CE2-BE94-4343-A1C9-4A53E3D2B2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10D037E-58F7-4ED1-A79A-9DDE171E12CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5488,10 +5488,55 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_coal_st_G100000107649_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107651_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100734-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107652_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100730-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100733-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000105928_rf</t>
   </si>
   <si>
-    <t>ep_coal_st_G100000100733-CHP_rf</t>
+    <t>ep_coal_sc_G100000104991-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107654_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100728-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100727-CHP_rf</t>
   </si>
   <si>
     <t>ep_coal_st_G100000100731-CHP_rf</t>
@@ -5500,103 +5545,58 @@
     <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_st_G100000107651_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100734-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107649_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
+    <t>ep_coal_usc_G100000107653_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100729-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000100722_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100726-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100725-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100735-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100732-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100001000616_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000106102-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110372_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000111550-CHP_rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_st_G100000111550-CHP_rf</t>
-  </si>
-  <si>
     <t>ep_coal_st_G100000107650_rf</t>
   </si>
   <si>
-    <t>ep_coal_sc_G100001000616_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000106102-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110372_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100726-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107653_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100729-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000100722_rf</t>
+    <t>ep_coal_st_G100000105920_rf</t>
   </si>
   <si>
     <t>ep_coal_sc_G100000107859_rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105920_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100727-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100728-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100730-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107652_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100732-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100725-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100735-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000104991-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107654_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6909,7 +6909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C846FD6-271F-4F66-AF33-82A71C8B444F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7D7317-4E4B-4D58-A32B-59D0FE8562CB}">
   <dimension ref="B2:AG1615"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44008,7 +44008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65935634-3F7D-4564-899F-4EB106F3448F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992FD1E1-8A23-48C4-96CE-03E6AC5FF9EA}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -58269,7 +58269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2E71F3-42DB-44CC-880E-1CDB0F36164D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B614D54C-2AD0-4714-A2DE-AB42DB7D9E9A}">
   <dimension ref="B2:Q248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61746,7 +61746,7 @@
         <v>1801</v>
       </c>
       <c r="P212" t="s">
-        <v>1769</v>
+        <v>1781</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -61760,7 +61760,7 @@
         <v>1802</v>
       </c>
       <c r="P213" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -61774,10 +61774,10 @@
         <v>1803</v>
       </c>
       <c r="P214" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="Q214">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -61788,10 +61788,10 @@
         <v>1804</v>
       </c>
       <c r="P215" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
       <c r="Q215">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -61830,7 +61830,7 @@
         <v>1807</v>
       </c>
       <c r="P218" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -61844,10 +61844,10 @@
         <v>1808</v>
       </c>
       <c r="P219" t="s">
-        <v>1785</v>
+        <v>1769</v>
       </c>
       <c r="Q219">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -61858,10 +61858,10 @@
         <v>1809</v>
       </c>
       <c r="P220" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
       <c r="Q220">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -61872,10 +61872,10 @@
         <v>1810</v>
       </c>
       <c r="P221" t="s">
-        <v>1785</v>
+        <v>1762</v>
       </c>
       <c r="Q221">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="222" spans="14:17" x14ac:dyDescent="0.45">
@@ -61900,10 +61900,10 @@
         <v>1812</v>
       </c>
       <c r="P223" t="s">
-        <v>1769</v>
+        <v>1782</v>
       </c>
       <c r="Q223">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="224" spans="14:17" x14ac:dyDescent="0.45">
@@ -61914,10 +61914,10 @@
         <v>1813</v>
       </c>
       <c r="P224" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="Q224">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="225" spans="14:17" x14ac:dyDescent="0.45">
@@ -61928,10 +61928,10 @@
         <v>1814</v>
       </c>
       <c r="P225" t="s">
-        <v>1760</v>
+        <v>1771</v>
       </c>
       <c r="Q225">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="226" spans="14:17" x14ac:dyDescent="0.45">
@@ -61942,10 +61942,10 @@
         <v>1815</v>
       </c>
       <c r="P226" t="s">
-        <v>1786</v>
+        <v>1776</v>
       </c>
       <c r="Q226">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="227" spans="14:17" x14ac:dyDescent="0.45">
@@ -61956,7 +61956,7 @@
         <v>1816</v>
       </c>
       <c r="P227" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -61998,10 +61998,10 @@
         <v>1819</v>
       </c>
       <c r="P230" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="Q230">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="231" spans="14:17" x14ac:dyDescent="0.45">
@@ -62012,10 +62012,10 @@
         <v>1820</v>
       </c>
       <c r="P231" t="s">
-        <v>1796</v>
+        <v>1781</v>
       </c>
       <c r="Q231">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="232" spans="14:17" x14ac:dyDescent="0.45">
@@ -62026,7 +62026,7 @@
         <v>1821</v>
       </c>
       <c r="P232" t="s">
-        <v>1769</v>
+        <v>1786</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -62040,10 +62040,10 @@
         <v>1822</v>
       </c>
       <c r="P233" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
       <c r="Q233">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -62054,10 +62054,10 @@
         <v>1823</v>
       </c>
       <c r="P234" t="s">
-        <v>1761</v>
+        <v>1786</v>
       </c>
       <c r="Q234">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -62110,7 +62110,7 @@
         <v>1827</v>
       </c>
       <c r="P238" t="s">
-        <v>1781</v>
+        <v>1769</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -62124,10 +62124,10 @@
         <v>1828</v>
       </c>
       <c r="P239" t="s">
-        <v>1776</v>
+        <v>1793</v>
       </c>
       <c r="Q239">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="240" spans="14:17" x14ac:dyDescent="0.45">
@@ -62138,7 +62138,7 @@
         <v>1829</v>
       </c>
       <c r="P240" t="s">
-        <v>1786</v>
+        <v>1760</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -62152,7 +62152,7 @@
         <v>1830</v>
       </c>
       <c r="P241" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -62166,10 +62166,10 @@
         <v>1831</v>
       </c>
       <c r="P242" t="s">
-        <v>1786</v>
+        <v>1797</v>
       </c>
       <c r="Q242">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="243" spans="14:17" x14ac:dyDescent="0.45">
@@ -62180,7 +62180,7 @@
         <v>1832</v>
       </c>
       <c r="P243" t="s">
-        <v>1793</v>
+        <v>1781</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -62194,7 +62194,7 @@
         <v>1833</v>
       </c>
       <c r="P244" t="s">
-        <v>1781</v>
+        <v>1769</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -62211,7 +62211,7 @@
         <v>1782</v>
       </c>
       <c r="Q245">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -62222,7 +62222,7 @@
         <v>1835</v>
       </c>
       <c r="P246" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Q246">
         <v>0.95</v>
@@ -62236,7 +62236,7 @@
         <v>1836</v>
       </c>
       <c r="P247" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="Q247">
         <v>0.95</v>
@@ -62250,7 +62250,7 @@
         <v>1837</v>
       </c>
       <c r="P248" t="s">
-        <v>1771</v>
+        <v>1796</v>
       </c>
       <c r="Q248">
         <v>0.95</v>
@@ -62262,7 +62262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A12C32-7A7F-4AB2-9779-180FBF0FA173}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C655016-3581-483A-B753-56A4996BB958}">
   <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10D037E-58F7-4ED1-A79A-9DDE171E12CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0B7DAF-417E-4B84-8E97-67D66B0A04E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5488,22 +5488,88 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_coal_st_G100000100731-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100730-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107652_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100726-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107653_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100729-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000100722_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000107649_rf</t>
   </si>
   <si>
     <t>ep_coal_st_G100000107651_rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
-  </si>
-  <si>
     <t>ep_coal_st_G100000100734-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_st_G100000107652_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100730-CHP_rf</t>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000111550-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107650_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100732-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100725-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100735-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000106102-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100001000616_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110372_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000107859_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105920_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100727-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100728-CHP_rf</t>
   </si>
   <si>
     <t>ep_coal_st_G100000100733-CHP_rf</t>
@@ -5512,91 +5578,25 @@
     <t>ep_coal_st_G100000105928_rf</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107654_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
+  </si>
+  <si>
     <t>ep_coal_sc_G100000104991-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107654_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100728-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100727-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100731-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107653_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100729-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000100722_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100726-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100725-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100735-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100732-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100001000616_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000106102-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110372_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000111550-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107650_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105920_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000107859_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6909,7 +6909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7D7317-4E4B-4D58-A32B-59D0FE8562CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D4C1A1-1CA4-4F43-BEDD-564D04A7C44E}">
   <dimension ref="B2:AG1615"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44008,7 +44008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992FD1E1-8A23-48C4-96CE-03E6AC5FF9EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41D2B9A-3F2A-405A-9336-395DFF24FD0C}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -58269,7 +58269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B614D54C-2AD0-4714-A2DE-AB42DB7D9E9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4F07833-AEB8-4B72-AF5A-03F580422931}">
   <dimension ref="B2:Q248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61746,7 +61746,7 @@
         <v>1801</v>
       </c>
       <c r="P212" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q212">
         <v>0.85</v>
@@ -61760,7 +61760,7 @@
         <v>1802</v>
       </c>
       <c r="P213" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -61774,10 +61774,10 @@
         <v>1803</v>
       </c>
       <c r="P214" t="s">
-        <v>1785</v>
+        <v>1781</v>
       </c>
       <c r="Q214">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="215" spans="14:17" x14ac:dyDescent="0.45">
@@ -61844,10 +61844,10 @@
         <v>1808</v>
       </c>
       <c r="P219" t="s">
-        <v>1769</v>
+        <v>1785</v>
       </c>
       <c r="Q219">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -61858,7 +61858,7 @@
         <v>1809</v>
       </c>
       <c r="P220" t="s">
-        <v>1793</v>
+        <v>1781</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -61872,10 +61872,10 @@
         <v>1810</v>
       </c>
       <c r="P221" t="s">
-        <v>1762</v>
+        <v>1781</v>
       </c>
       <c r="Q221">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="222" spans="14:17" x14ac:dyDescent="0.45">
@@ -61886,7 +61886,7 @@
         <v>1811</v>
       </c>
       <c r="P222" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -61900,7 +61900,7 @@
         <v>1812</v>
       </c>
       <c r="P223" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="Q223">
         <v>0.95</v>
@@ -61914,7 +61914,7 @@
         <v>1813</v>
       </c>
       <c r="P224" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="Q224">
         <v>0.95</v>
@@ -61928,10 +61928,10 @@
         <v>1814</v>
       </c>
       <c r="P225" t="s">
-        <v>1771</v>
+        <v>1785</v>
       </c>
       <c r="Q225">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="226" spans="14:17" x14ac:dyDescent="0.45">
@@ -61942,10 +61942,10 @@
         <v>1815</v>
       </c>
       <c r="P226" t="s">
-        <v>1776</v>
+        <v>1781</v>
       </c>
       <c r="Q226">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="227" spans="14:17" x14ac:dyDescent="0.45">
@@ -61998,10 +61998,10 @@
         <v>1819</v>
       </c>
       <c r="P230" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="Q230">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="231" spans="14:17" x14ac:dyDescent="0.45">
@@ -62012,7 +62012,7 @@
         <v>1820</v>
       </c>
       <c r="P231" t="s">
-        <v>1781</v>
+        <v>1769</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -62026,7 +62026,7 @@
         <v>1821</v>
       </c>
       <c r="P232" t="s">
-        <v>1786</v>
+        <v>1760</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -62040,10 +62040,10 @@
         <v>1822</v>
       </c>
       <c r="P233" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="Q233">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -62054,10 +62054,10 @@
         <v>1823</v>
       </c>
       <c r="P234" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="Q234">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -62068,10 +62068,10 @@
         <v>1824</v>
       </c>
       <c r="P235" t="s">
-        <v>1786</v>
+        <v>1761</v>
       </c>
       <c r="Q235">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="236" spans="14:17" x14ac:dyDescent="0.45">
@@ -62082,7 +62082,7 @@
         <v>1825</v>
       </c>
       <c r="P236" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="Q236">
         <v>0.85</v>
@@ -62096,7 +62096,7 @@
         <v>1826</v>
       </c>
       <c r="P237" t="s">
-        <v>1786</v>
+        <v>1769</v>
       </c>
       <c r="Q237">
         <v>0.85</v>
@@ -62110,7 +62110,7 @@
         <v>1827</v>
       </c>
       <c r="P238" t="s">
-        <v>1769</v>
+        <v>1786</v>
       </c>
       <c r="Q238">
         <v>0.85</v>
@@ -62124,7 +62124,7 @@
         <v>1828</v>
       </c>
       <c r="P239" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="Q239">
         <v>0.85</v>
@@ -62138,7 +62138,7 @@
         <v>1829</v>
       </c>
       <c r="P240" t="s">
-        <v>1760</v>
+        <v>1786</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -62152,7 +62152,7 @@
         <v>1830</v>
       </c>
       <c r="P241" t="s">
-        <v>1785</v>
+        <v>1769</v>
       </c>
       <c r="Q241">
         <v>0.85</v>
@@ -62166,7 +62166,7 @@
         <v>1831</v>
       </c>
       <c r="P242" t="s">
-        <v>1797</v>
+        <v>1776</v>
       </c>
       <c r="Q242">
         <v>0.95</v>
@@ -62180,10 +62180,10 @@
         <v>1832</v>
       </c>
       <c r="P243" t="s">
-        <v>1781</v>
+        <v>1795</v>
       </c>
       <c r="Q243">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="244" spans="14:17" x14ac:dyDescent="0.45">
@@ -62194,10 +62194,10 @@
         <v>1833</v>
       </c>
       <c r="P244" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="Q244">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="245" spans="14:17" x14ac:dyDescent="0.45">
@@ -62208,7 +62208,7 @@
         <v>1834</v>
       </c>
       <c r="P245" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="Q245">
         <v>0.85</v>
@@ -62222,7 +62222,7 @@
         <v>1835</v>
       </c>
       <c r="P246" t="s">
-        <v>1792</v>
+        <v>1782</v>
       </c>
       <c r="Q246">
         <v>0.95</v>
@@ -62236,7 +62236,7 @@
         <v>1836</v>
       </c>
       <c r="P247" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="Q247">
         <v>0.95</v>
@@ -62250,10 +62250,10 @@
         <v>1837</v>
       </c>
       <c r="P248" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="Q248">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -62262,7 +62262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C655016-3581-483A-B753-56A4996BB958}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30145766-428E-4A6B-A0FD-E78AD1C3930B}">
   <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0B7DAF-417E-4B84-8E97-67D66B0A04E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA03DCC2-0D5E-49ED-8E72-F3C55ACE09F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5488,42 +5488,57 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000100731-CHP_rf</t>
   </si>
   <si>
+    <t>ep_coal_st_G100000107651_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107649_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100734-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100728-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100727-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000100730-CHP_rf</t>
   </si>
   <si>
     <t>ep_coal_st_G100000107652_rf</t>
   </si>
   <si>
+    <t>ep_coal_sc_G100001000616_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000106102-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110372_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107653_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100729-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000100726-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_usc_G100000107653_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100729-CHP_rf</t>
-  </si>
-  <si>
     <t>ep_coal_sc_G100000100722_rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107649_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107651_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100734-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
   </si>
   <si>
@@ -5533,70 +5548,55 @@
     <t>ep_coal_st_G100000107650_rf</t>
   </si>
   <si>
+    <t>ep_coal_sc_G100000107859_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105920_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105928_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100733-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000104991-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107654_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100725-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000100732-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_st_G100000100725-CHP_rf</t>
-  </si>
-  <si>
     <t>ep_coal_st_G100000100735-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000106102-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100001000616_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110372_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000107859_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105920_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100727-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100728-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100733-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105928_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107654_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000104991-CHP_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6909,7 +6909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D4C1A1-1CA4-4F43-BEDD-564D04A7C44E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AEF9A81-8DA1-4F02-8A81-6E47D819562D}">
   <dimension ref="B2:AG1615"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44008,7 +44008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41D2B9A-3F2A-405A-9336-395DFF24FD0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB13F8E-15CC-4ECE-BC2B-6086EDE2C0EA}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -58269,7 +58269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4F07833-AEB8-4B72-AF5A-03F580422931}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84825513-0F28-474F-ADF4-5AAD55574868}">
   <dimension ref="B2:Q248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61746,10 +61746,10 @@
         <v>1801</v>
       </c>
       <c r="P212" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="Q212">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="213" spans="14:17" x14ac:dyDescent="0.45">
@@ -61788,7 +61788,7 @@
         <v>1804</v>
       </c>
       <c r="P215" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q215">
         <v>0.85</v>
@@ -61802,7 +61802,7 @@
         <v>1805</v>
       </c>
       <c r="P216" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q216">
         <v>0.85</v>
@@ -61816,10 +61816,10 @@
         <v>1806</v>
       </c>
       <c r="P217" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="Q217">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="218" spans="14:17" x14ac:dyDescent="0.45">
@@ -61844,10 +61844,10 @@
         <v>1808</v>
       </c>
       <c r="P219" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="Q219">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="220" spans="14:17" x14ac:dyDescent="0.45">
@@ -61858,7 +61858,7 @@
         <v>1809</v>
       </c>
       <c r="P220" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -61886,7 +61886,7 @@
         <v>1811</v>
       </c>
       <c r="P222" t="s">
-        <v>1786</v>
+        <v>1769</v>
       </c>
       <c r="Q222">
         <v>0.85</v>
@@ -61900,10 +61900,10 @@
         <v>1812</v>
       </c>
       <c r="P223" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="Q223">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="224" spans="14:17" x14ac:dyDescent="0.45">
@@ -61914,10 +61914,10 @@
         <v>1813</v>
       </c>
       <c r="P224" t="s">
-        <v>1797</v>
+        <v>1760</v>
       </c>
       <c r="Q224">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="225" spans="14:17" x14ac:dyDescent="0.45">
@@ -61928,7 +61928,7 @@
         <v>1814</v>
       </c>
       <c r="P225" t="s">
-        <v>1785</v>
+        <v>1781</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -61942,7 +61942,7 @@
         <v>1815</v>
       </c>
       <c r="P226" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q226">
         <v>0.85</v>
@@ -61984,10 +61984,10 @@
         <v>1818</v>
       </c>
       <c r="P229" t="s">
-        <v>1786</v>
+        <v>1797</v>
       </c>
       <c r="Q229">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -61998,7 +61998,7 @@
         <v>1819</v>
       </c>
       <c r="P230" t="s">
-        <v>1793</v>
+        <v>1785</v>
       </c>
       <c r="Q230">
         <v>0.85</v>
@@ -62012,7 +62012,7 @@
         <v>1820</v>
       </c>
       <c r="P231" t="s">
-        <v>1769</v>
+        <v>1781</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -62026,7 +62026,7 @@
         <v>1821</v>
       </c>
       <c r="P232" t="s">
-        <v>1760</v>
+        <v>1782</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -62040,7 +62040,7 @@
         <v>1822</v>
       </c>
       <c r="P233" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="Q233">
         <v>0.95</v>
@@ -62054,10 +62054,10 @@
         <v>1823</v>
       </c>
       <c r="P234" t="s">
-        <v>1796</v>
+        <v>1769</v>
       </c>
       <c r="Q234">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -62082,10 +62082,10 @@
         <v>1825</v>
       </c>
       <c r="P236" t="s">
-        <v>1782</v>
+        <v>1792</v>
       </c>
       <c r="Q236">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="237" spans="14:17" x14ac:dyDescent="0.45">
@@ -62124,10 +62124,10 @@
         <v>1828</v>
       </c>
       <c r="P239" t="s">
-        <v>1786</v>
+        <v>1776</v>
       </c>
       <c r="Q239">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="240" spans="14:17" x14ac:dyDescent="0.45">
@@ -62138,7 +62138,7 @@
         <v>1829</v>
       </c>
       <c r="P240" t="s">
-        <v>1786</v>
+        <v>1793</v>
       </c>
       <c r="Q240">
         <v>0.85</v>
@@ -62152,10 +62152,10 @@
         <v>1830</v>
       </c>
       <c r="P241" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="Q241">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="242" spans="14:17" x14ac:dyDescent="0.45">
@@ -62166,7 +62166,7 @@
         <v>1831</v>
       </c>
       <c r="P242" t="s">
-        <v>1776</v>
+        <v>1762</v>
       </c>
       <c r="Q242">
         <v>0.95</v>
@@ -62180,10 +62180,10 @@
         <v>1832</v>
       </c>
       <c r="P243" t="s">
-        <v>1795</v>
+        <v>1781</v>
       </c>
       <c r="Q243">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="244" spans="14:17" x14ac:dyDescent="0.45">
@@ -62194,7 +62194,7 @@
         <v>1833</v>
       </c>
       <c r="P244" t="s">
-        <v>1771</v>
+        <v>1782</v>
       </c>
       <c r="Q244">
         <v>0.95</v>
@@ -62208,10 +62208,10 @@
         <v>1834</v>
       </c>
       <c r="P245" t="s">
-        <v>1781</v>
+        <v>1795</v>
       </c>
       <c r="Q245">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -62222,10 +62222,10 @@
         <v>1835</v>
       </c>
       <c r="P246" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="Q246">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="247" spans="14:17" x14ac:dyDescent="0.45">
@@ -62236,10 +62236,10 @@
         <v>1836</v>
       </c>
       <c r="P247" t="s">
-        <v>1762</v>
+        <v>1786</v>
       </c>
       <c r="Q247">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -62250,7 +62250,7 @@
         <v>1837</v>
       </c>
       <c r="P248" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="Q248">
         <v>0.85</v>
@@ -62262,7 +62262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30145766-428E-4A6B-A0FD-E78AD1C3930B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20644731-148A-4C7D-BB39-2F27F1EB2D1B}">
   <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA03DCC2-0D5E-49ED-8E72-F3C55ACE09F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAC7A0F-B21B-414F-A65F-95FDA5339B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5488,115 +5488,115 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_coal_st_G100000100730-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107652_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100733-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105928_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107653_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100729-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000100722_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100726-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000111550-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107650_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100725-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100735-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100732-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
   </si>
   <si>
+    <t>ep_coal_st_G100000107651_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107649_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100734-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100001000616_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000106102-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110372_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000104991-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107654_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100728-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100727-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000107859_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105920_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000100731-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107651_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107649_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100734-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100728-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100727-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100730-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107652_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100001000616_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000106102-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110372_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107653_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100729-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100726-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000100722_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000111550-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107650_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000107859_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105920_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105928_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100733-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000104991-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107654_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100725-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100732-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100735-CHP_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6909,7 +6909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AEF9A81-8DA1-4F02-8A81-6E47D819562D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868590DC-006B-4F98-9B2B-1979674B0941}">
   <dimension ref="B2:AG1615"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44008,7 +44008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB13F8E-15CC-4ECE-BC2B-6086EDE2C0EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEEE356-8BDA-4851-AB38-0C29777FF3A5}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -58269,7 +58269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84825513-0F28-474F-ADF4-5AAD55574868}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5469935-34D9-4B56-9CF5-58F85DC0B070}">
   <dimension ref="B2:Q248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61746,10 +61746,10 @@
         <v>1801</v>
       </c>
       <c r="P212" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
       <c r="Q212">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="213" spans="14:17" x14ac:dyDescent="0.45">
@@ -61760,7 +61760,7 @@
         <v>1802</v>
       </c>
       <c r="P213" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -61774,7 +61774,7 @@
         <v>1803</v>
       </c>
       <c r="P214" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q214">
         <v>0.85</v>
@@ -61788,7 +61788,7 @@
         <v>1804</v>
       </c>
       <c r="P215" t="s">
-        <v>1781</v>
+        <v>1769</v>
       </c>
       <c r="Q215">
         <v>0.85</v>
@@ -61802,7 +61802,7 @@
         <v>1805</v>
       </c>
       <c r="P216" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q216">
         <v>0.85</v>
@@ -61816,10 +61816,10 @@
         <v>1806</v>
       </c>
       <c r="P217" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="Q217">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="218" spans="14:17" x14ac:dyDescent="0.45">
@@ -61858,7 +61858,7 @@
         <v>1809</v>
       </c>
       <c r="P220" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="Q220">
         <v>0.85</v>
@@ -61886,10 +61886,10 @@
         <v>1811</v>
       </c>
       <c r="P222" t="s">
-        <v>1769</v>
+        <v>1797</v>
       </c>
       <c r="Q222">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="223" spans="14:17" x14ac:dyDescent="0.45">
@@ -61900,7 +61900,7 @@
         <v>1812</v>
       </c>
       <c r="P223" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="Q223">
         <v>0.85</v>
@@ -61914,7 +61914,7 @@
         <v>1813</v>
       </c>
       <c r="P224" t="s">
-        <v>1760</v>
+        <v>1786</v>
       </c>
       <c r="Q224">
         <v>0.85</v>
@@ -61928,7 +61928,7 @@
         <v>1814</v>
       </c>
       <c r="P225" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q225">
         <v>0.85</v>
@@ -61942,10 +61942,10 @@
         <v>1815</v>
       </c>
       <c r="P226" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="Q226">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="227" spans="14:17" x14ac:dyDescent="0.45">
@@ -61956,7 +61956,7 @@
         <v>1816</v>
       </c>
       <c r="P227" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q227">
         <v>0.85</v>
@@ -61970,7 +61970,7 @@
         <v>1817</v>
       </c>
       <c r="P228" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q228">
         <v>0.85</v>
@@ -61984,10 +61984,10 @@
         <v>1818</v>
       </c>
       <c r="P229" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="Q229">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="230" spans="14:17" x14ac:dyDescent="0.45">
@@ -62001,7 +62001,7 @@
         <v>1785</v>
       </c>
       <c r="Q230">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="231" spans="14:17" x14ac:dyDescent="0.45">
@@ -62012,7 +62012,7 @@
         <v>1820</v>
       </c>
       <c r="P231" t="s">
-        <v>1781</v>
+        <v>1769</v>
       </c>
       <c r="Q231">
         <v>0.85</v>
@@ -62026,7 +62026,7 @@
         <v>1821</v>
       </c>
       <c r="P232" t="s">
-        <v>1782</v>
+        <v>1793</v>
       </c>
       <c r="Q232">
         <v>0.85</v>
@@ -62040,10 +62040,10 @@
         <v>1822</v>
       </c>
       <c r="P233" t="s">
-        <v>1796</v>
+        <v>1760</v>
       </c>
       <c r="Q233">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="234" spans="14:17" x14ac:dyDescent="0.45">
@@ -62054,7 +62054,7 @@
         <v>1823</v>
       </c>
       <c r="P234" t="s">
-        <v>1769</v>
+        <v>1793</v>
       </c>
       <c r="Q234">
         <v>0.85</v>
@@ -62068,10 +62068,10 @@
         <v>1824</v>
       </c>
       <c r="P235" t="s">
-        <v>1761</v>
+        <v>1781</v>
       </c>
       <c r="Q235">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="236" spans="14:17" x14ac:dyDescent="0.45">
@@ -62082,7 +62082,7 @@
         <v>1825</v>
       </c>
       <c r="P236" t="s">
-        <v>1792</v>
+        <v>1782</v>
       </c>
       <c r="Q236">
         <v>0.95</v>
@@ -62096,10 +62096,10 @@
         <v>1826</v>
       </c>
       <c r="P237" t="s">
-        <v>1769</v>
+        <v>1795</v>
       </c>
       <c r="Q237">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="238" spans="14:17" x14ac:dyDescent="0.45">
@@ -62110,10 +62110,10 @@
         <v>1827</v>
       </c>
       <c r="P238" t="s">
-        <v>1786</v>
+        <v>1771</v>
       </c>
       <c r="Q238">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="239" spans="14:17" x14ac:dyDescent="0.45">
@@ -62124,7 +62124,7 @@
         <v>1828</v>
       </c>
       <c r="P239" t="s">
-        <v>1776</v>
+        <v>1762</v>
       </c>
       <c r="Q239">
         <v>0.95</v>
@@ -62138,10 +62138,10 @@
         <v>1829</v>
       </c>
       <c r="P240" t="s">
-        <v>1793</v>
+        <v>1776</v>
       </c>
       <c r="Q240">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -62152,10 +62152,10 @@
         <v>1830</v>
       </c>
       <c r="P241" t="s">
-        <v>1771</v>
+        <v>1786</v>
       </c>
       <c r="Q241">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="242" spans="14:17" x14ac:dyDescent="0.45">
@@ -62166,10 +62166,10 @@
         <v>1831</v>
       </c>
       <c r="P242" t="s">
-        <v>1762</v>
+        <v>1786</v>
       </c>
       <c r="Q242">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="243" spans="14:17" x14ac:dyDescent="0.45">
@@ -62180,7 +62180,7 @@
         <v>1832</v>
       </c>
       <c r="P243" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -62194,10 +62194,10 @@
         <v>1833</v>
       </c>
       <c r="P244" t="s">
-        <v>1782</v>
+        <v>1769</v>
       </c>
       <c r="Q244">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="245" spans="14:17" x14ac:dyDescent="0.45">
@@ -62208,7 +62208,7 @@
         <v>1834</v>
       </c>
       <c r="P245" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="Q245">
         <v>0.95</v>
@@ -62222,10 +62222,10 @@
         <v>1835</v>
       </c>
       <c r="P246" t="s">
-        <v>1786</v>
+        <v>1761</v>
       </c>
       <c r="Q246">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="247" spans="14:17" x14ac:dyDescent="0.45">
@@ -62236,10 +62236,10 @@
         <v>1836</v>
       </c>
       <c r="P247" t="s">
-        <v>1786</v>
+        <v>1796</v>
       </c>
       <c r="Q247">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -62262,7 +62262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20644731-148A-4C7D-BB39-2F27F1EB2D1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987A81E6-152F-4305-A3E2-9C35689C747F}">
   <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAC7A0F-B21B-414F-A65F-95FDA5339B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F883E07E-8E1D-4623-A147-D095B4647F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5488,16 +5488,106 @@
     <t>co2_Pulawy_POL</t>
   </si>
   <si>
+    <t>ep_coal_st_G100000100731-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100733-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105928_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000107859_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000105920_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107652_rf</t>
+  </si>
+  <si>
     <t>ep_coal_st_G100000100730-CHP_rf</t>
   </si>
   <si>
-    <t>ep_coal_st_G100000107652_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100733-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105928_rf</t>
+    <t>ep_coal_st_G100000100732-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100725-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100735-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107651_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100734-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107649_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000104991-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000107654_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100728-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100727-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100001000616_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_sc_G100000106102-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_usc_G100000110372_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000111550-CHP_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000107650_rf</t>
+  </si>
+  <si>
+    <t>ep_coal_st_G100000100726-CHP_rf</t>
   </si>
   <si>
     <t>ep_coal_usc_G100000107653_rf</t>
@@ -5507,96 +5597,6 @@
   </si>
   <si>
     <t>ep_coal_sc_G100000100722_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100726-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000111550-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107650_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400812-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100725-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100735-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100732-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401338-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107651_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000107649_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100734-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401342-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100001000616_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000106102-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000110372_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000104991-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_usc_G100000107654_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000410414-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401072_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000401340_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100000406283_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401341-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100728-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100727-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_sc_G100000107859_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000105920_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000401337-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_c_gas_combined_cycle_G100001030927_rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000406286-CHP_rf</t>
-  </si>
-  <si>
-    <t>ep_coal_st_G100000100731-CHP_rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -6909,7 +6909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868590DC-006B-4F98-9B2B-1979674B0941}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB897DB-75CA-4F79-89A1-4A59FD409C0D}">
   <dimension ref="B2:AG1615"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44008,7 +44008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEEE356-8BDA-4851-AB38-0C29777FF3A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FBAF7D-EBC2-4F11-836E-37AC7543E7E4}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -58269,7 +58269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5469935-34D9-4B56-9CF5-58F85DC0B070}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53944FF-0039-48EA-A3EC-E1964A9AC04D}">
   <dimension ref="B2:Q248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61760,7 +61760,7 @@
         <v>1802</v>
       </c>
       <c r="P213" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q213">
         <v>0.85</v>
@@ -61774,7 +61774,7 @@
         <v>1803</v>
       </c>
       <c r="P214" t="s">
-        <v>1786</v>
+        <v>1769</v>
       </c>
       <c r="Q214">
         <v>0.85</v>
@@ -61788,10 +61788,10 @@
         <v>1804</v>
       </c>
       <c r="P215" t="s">
-        <v>1769</v>
+        <v>1796</v>
       </c>
       <c r="Q215">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="216" spans="14:17" x14ac:dyDescent="0.45">
@@ -61802,10 +61802,10 @@
         <v>1805</v>
       </c>
       <c r="P216" t="s">
-        <v>1781</v>
+        <v>1792</v>
       </c>
       <c r="Q216">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="217" spans="14:17" x14ac:dyDescent="0.45">
@@ -61816,10 +61816,10 @@
         <v>1806</v>
       </c>
       <c r="P217" t="s">
-        <v>1786</v>
+        <v>1761</v>
       </c>
       <c r="Q217">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="218" spans="14:17" x14ac:dyDescent="0.45">
@@ -61830,7 +61830,7 @@
         <v>1807</v>
       </c>
       <c r="P218" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="Q218">
         <v>0.85</v>
@@ -61844,7 +61844,7 @@
         <v>1808</v>
       </c>
       <c r="P219" t="s">
-        <v>1786</v>
+        <v>1769</v>
       </c>
       <c r="Q219">
         <v>0.85</v>
@@ -61858,10 +61858,10 @@
         <v>1809</v>
       </c>
       <c r="P220" t="s">
-        <v>1785</v>
+        <v>1776</v>
       </c>
       <c r="Q220">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="221" spans="14:17" x14ac:dyDescent="0.45">
@@ -61886,10 +61886,10 @@
         <v>1811</v>
       </c>
       <c r="P222" t="s">
-        <v>1797</v>
+        <v>1786</v>
       </c>
       <c r="Q222">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="223" spans="14:17" x14ac:dyDescent="0.45">
@@ -61942,7 +61942,7 @@
         <v>1815</v>
       </c>
       <c r="P226" t="s">
-        <v>1792</v>
+        <v>1785</v>
       </c>
       <c r="Q226">
         <v>0.95</v>
@@ -61970,7 +61970,7 @@
         <v>1817</v>
       </c>
       <c r="P228" t="s">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="Q228">
         <v>0.85</v>
@@ -61984,7 +61984,7 @@
         <v>1818</v>
       </c>
       <c r="P229" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="Q229">
         <v>0.85</v>
@@ -61998,7 +61998,7 @@
         <v>1819</v>
       </c>
       <c r="P230" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
       <c r="Q230">
         <v>0.95</v>
@@ -62012,10 +62012,10 @@
         <v>1820</v>
       </c>
       <c r="P231" t="s">
-        <v>1769</v>
+        <v>1762</v>
       </c>
       <c r="Q231">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="232" spans="14:17" x14ac:dyDescent="0.45">
@@ -62026,10 +62026,10 @@
         <v>1821</v>
       </c>
       <c r="P232" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="Q232">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="233" spans="14:17" x14ac:dyDescent="0.45">
@@ -62040,7 +62040,7 @@
         <v>1822</v>
       </c>
       <c r="P233" t="s">
-        <v>1760</v>
+        <v>1793</v>
       </c>
       <c r="Q233">
         <v>0.85</v>
@@ -62054,10 +62054,10 @@
         <v>1823</v>
       </c>
       <c r="P234" t="s">
-        <v>1793</v>
+        <v>1771</v>
       </c>
       <c r="Q234">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="235" spans="14:17" x14ac:dyDescent="0.45">
@@ -62082,10 +62082,10 @@
         <v>1825</v>
       </c>
       <c r="P236" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="Q236">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="237" spans="14:17" x14ac:dyDescent="0.45">
@@ -62096,10 +62096,10 @@
         <v>1826</v>
       </c>
       <c r="P237" t="s">
-        <v>1795</v>
+        <v>1786</v>
       </c>
       <c r="Q237">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="238" spans="14:17" x14ac:dyDescent="0.45">
@@ -62110,10 +62110,10 @@
         <v>1827</v>
       </c>
       <c r="P238" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="Q238">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="239" spans="14:17" x14ac:dyDescent="0.45">
@@ -62124,10 +62124,10 @@
         <v>1828</v>
       </c>
       <c r="P239" t="s">
-        <v>1762</v>
+        <v>1793</v>
       </c>
       <c r="Q239">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="240" spans="14:17" x14ac:dyDescent="0.45">
@@ -62138,10 +62138,10 @@
         <v>1829</v>
       </c>
       <c r="P240" t="s">
-        <v>1776</v>
+        <v>1760</v>
       </c>
       <c r="Q240">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="241" spans="14:17" x14ac:dyDescent="0.45">
@@ -62152,10 +62152,10 @@
         <v>1830</v>
       </c>
       <c r="P241" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="Q241">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="242" spans="14:17" x14ac:dyDescent="0.45">
@@ -62166,10 +62166,10 @@
         <v>1831</v>
       </c>
       <c r="P242" t="s">
-        <v>1786</v>
+        <v>1797</v>
       </c>
       <c r="Q242">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="243" spans="14:17" x14ac:dyDescent="0.45">
@@ -62180,7 +62180,7 @@
         <v>1832</v>
       </c>
       <c r="P243" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="Q243">
         <v>0.85</v>
@@ -62194,7 +62194,7 @@
         <v>1833</v>
       </c>
       <c r="P244" t="s">
-        <v>1769</v>
+        <v>1781</v>
       </c>
       <c r="Q244">
         <v>0.85</v>
@@ -62208,10 +62208,10 @@
         <v>1834</v>
       </c>
       <c r="P245" t="s">
-        <v>1792</v>
+        <v>1786</v>
       </c>
       <c r="Q245">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="246" spans="14:17" x14ac:dyDescent="0.45">
@@ -62222,10 +62222,10 @@
         <v>1835</v>
       </c>
       <c r="P246" t="s">
-        <v>1761</v>
+        <v>1781</v>
       </c>
       <c r="Q246">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="247" spans="14:17" x14ac:dyDescent="0.45">
@@ -62236,10 +62236,10 @@
         <v>1836</v>
       </c>
       <c r="P247" t="s">
-        <v>1796</v>
+        <v>1786</v>
       </c>
       <c r="Q247">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="248" spans="14:17" x14ac:dyDescent="0.45">
@@ -62262,7 +62262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987A81E6-152F-4305-A3E2-9C35689C747F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76D6C2-1143-40FD-8B57-4B5A32C6D46D}">
   <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
